--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.00256628195114</v>
+        <v>3.737917020817061</v>
       </c>
       <c r="D2" t="n">
-        <v>24.19275345616337</v>
+        <v>3.931322436626548</v>
       </c>
       <c r="E2" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F2" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>86.95363547444248</v>
+        <v>14.1299657645969</v>
       </c>
       <c r="D3" t="n">
-        <v>88.03007273514896</v>
+        <v>14.30488681946171</v>
       </c>
       <c r="E3" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F3" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>94.11031499728864</v>
+        <v>15.2929261870594</v>
       </c>
       <c r="D4" t="n">
-        <v>95.11272086670583</v>
+        <v>15.4558171408397</v>
       </c>
       <c r="E4" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F4" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.00194212575859</v>
+        <v>2.112815595435771</v>
       </c>
       <c r="D5" t="n">
-        <v>12.89839155868271</v>
+        <v>2.095988628285941</v>
       </c>
       <c r="E5" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F5" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.29384753056672</v>
+        <v>5.247750223717092</v>
       </c>
       <c r="D6" t="n">
-        <v>32.13378486199707</v>
+        <v>5.221740040074525</v>
       </c>
       <c r="E6" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F6" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.08318666556931</v>
+        <v>9.763517833155014</v>
       </c>
       <c r="D7" t="n">
-        <v>59.68066413889394</v>
+        <v>9.698107922570266</v>
       </c>
       <c r="E7" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F7" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.84401398845144</v>
+        <v>11.51215227312336</v>
       </c>
       <c r="D8" t="n">
-        <v>70.50122220062347</v>
+        <v>11.45644860760132</v>
       </c>
       <c r="E8" t="n">
-        <v>29.58666517767185</v>
+        <v>4.807833091371676</v>
       </c>
       <c r="F8" t="n">
-        <v>29.77499065913464</v>
+        <v>4.838435982109379</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
